--- a/practice/answers/q014.xlsx
+++ b/practice/answers/q014.xlsx
@@ -1549,14 +1549,14 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="46" customHeight="1">
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>(b) Ninety percent of RMs had 2023 oat yields at or below about 117 bu/ac -- only the top tenth of RMs did better than that.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="46" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>(d) The mean (71.1) sits below the median (75.9), so the distribution is left-skewed: a tail of low-yield RMs pulls the mean down.</t>

--- a/practice/answers/q014.xlsx
+++ b/practice/answers/q014.xlsx
@@ -1,60 +1,124 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr/>
-  <workbookProtection/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2843139F94B2D70F19AE3F7D3970FD15C4D69C9B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCB12B9-0F93-4CFC-B96E-950EB5F1EC5F}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Answer" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+  <si>
+    <t>Oats 2023 (bu/ac)</t>
+  </si>
+  <si>
+    <t>Mean (a)</t>
+  </si>
+  <si>
+    <t>Median (a)</t>
+  </si>
+  <si>
+    <t>90th percentile (a)</t>
+  </si>
+  <si>
+    <t>Q1 (c)</t>
+  </si>
+  <si>
+    <t>Q3 (c)</t>
+  </si>
+  <si>
+    <t>IQR (c)</t>
+  </si>
+  <si>
+    <t>(b) Ninety percent of RMs had 2023 oat yields at or below about 117 bu/ac -- only the top tenth of RMs did better than that.</t>
+  </si>
+  <si>
+    <t>(d) The mean (71.1) sits below the median (75.9), so the distribution is left-skewed: a tail of low-yield RMs pulls the mean down.</t>
+  </si>
+  <si>
+    <t>Legend: colours mark question parts</t>
+  </si>
+  <si>
+    <t>Part (a)</t>
+  </si>
+  <si>
+    <t>Part (b)</t>
+  </si>
+  <si>
+    <t>Part (c)</t>
+  </si>
+  <si>
+    <t>Part (d)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFE2F3"/>
+        <fgColor rgb="FFCFE2F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,94 +134,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -445,1021 +451,1015 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A201"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Oats 2023 (bu/ac)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
         <v>55.1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:1">
+      <c r="A3">
         <v>81.8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>76.90000000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
         <v>80</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>19.6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
         <v>16</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>72.59999999999999</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>72.599999999999994</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9">
         <v>63.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:1">
+      <c r="A10">
         <v>77.5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:1">
+      <c r="A11">
         <v>93.3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:1">
+      <c r="A12">
         <v>14.7</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:1">
+      <c r="A13">
         <v>30</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:1">
+      <c r="A14">
         <v>15.7</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:1">
+      <c r="A15">
         <v>14.8</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:1">
+      <c r="A16">
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:1">
+      <c r="A17">
         <v>28.3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:1">
+      <c r="A18">
         <v>101.2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:1">
+      <c r="A19">
         <v>63.2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:1">
+      <c r="A20">
         <v>70.5</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:1">
+      <c r="A21">
         <v>28.3</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:1">
+      <c r="A22">
         <v>49.5</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:1">
+      <c r="A23">
         <v>9.4</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:1">
+      <c r="A24">
         <v>6</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:1">
+      <c r="A25">
         <v>11</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>20.1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
         <v>25</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:1">
+      <c r="A28">
         <v>61.1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>78.59999999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>78.599999999999994</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
         <v>62.9</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:1">
+      <c r="A31">
         <v>51.6</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>71.59999999999999</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>71.599999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
         <v>60.8</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:1">
+      <c r="A34">
         <v>54.7</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:1">
+      <c r="A35">
         <v>60</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:1">
+      <c r="A36">
         <v>15.8</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:1">
+      <c r="A37">
         <v>86.5</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:1">
+      <c r="A38">
         <v>68.2</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>79.40000000000001</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>64.09999999999999</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>79.400000000000006</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
         <v>61.8</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>84.40000000000001</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>65.09999999999999</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>84.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
         <v>70</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:1">
+      <c r="A45">
         <v>44.6</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
         <v>3.2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:1">
+      <c r="A49">
         <v>70</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:1">
+      <c r="A50">
         <v>48.8</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>79.59999999999999</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>79.599999999999994</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
         <v>82.8</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:1">
+      <c r="A53">
         <v>116.7</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:1">
+      <c r="A54">
         <v>87.2</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:1">
+      <c r="A55">
         <v>74.8</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:1">
+      <c r="A56">
         <v>22.8</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:1">
+      <c r="A57">
         <v>39.6</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>18.9</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
         <v>91.3</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>67.90000000000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>67.900000000000006</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
         <v>61.7</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>90.90000000000001</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>65.09999999999999</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>90.9</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>65.099999999999994</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
         <v>30.5</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:1">
+      <c r="A65">
         <v>3.6</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:1">
+      <c r="A66">
         <v>11</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:1">
+      <c r="A67">
         <v>95.5</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:1">
+      <c r="A68">
         <v>91</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>91.40000000000001</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>91.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
         <v>82.8</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>93.59999999999999</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>93.6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
         <v>120</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:1">
+      <c r="A73">
         <v>52.5</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:1">
+      <c r="A74">
         <v>49.9</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:1">
+      <c r="A75">
         <v>70</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:1">
+      <c r="A76">
         <v>45.1</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:1">
+      <c r="A77">
         <v>9.6</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:1">
+      <c r="A78">
         <v>3.8</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:1">
+      <c r="A79">
         <v>14.3</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>64.09999999999999</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>17.899999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
         <v>108</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:1">
+      <c r="A83">
         <v>80.3</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:1">
+      <c r="A84">
         <v>82.7</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>92.59999999999999</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>92.6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
         <v>87.3</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:1">
+      <c r="A87">
         <v>69.3</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:1">
+      <c r="A88">
         <v>7.1</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:1">
+      <c r="A89">
         <v>29.7</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:1">
+      <c r="A90">
         <v>24.1</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:1">
+      <c r="A91">
         <v>20</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:1">
+      <c r="A92">
         <v>66.7</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:1">
+      <c r="A93">
         <v>83.8</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:1">
+      <c r="A94">
         <v>97.7</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:1">
+      <c r="A95">
         <v>82.2</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:1">
+      <c r="A96">
         <v>99.5</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:1">
+      <c r="A97">
         <v>78</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="n">
+    <row r="98" spans="1:1">
+      <c r="A98">
         <v>15</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="n">
+    <row r="99" spans="1:1">
+      <c r="A99">
         <v>39</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="n">
+    <row r="100" spans="1:1">
+      <c r="A100">
         <v>35</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="n">
+    <row r="101" spans="1:1">
+      <c r="A101">
         <v>41.8</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="n">
+    <row r="102" spans="1:1">
+      <c r="A102">
         <v>57.6</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="n">
+    <row r="103" spans="1:1">
+      <c r="A103">
         <v>21</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="n">
+    <row r="104" spans="1:1">
+      <c r="A104">
         <v>55.7</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="n">
+    <row r="105" spans="1:1">
+      <c r="A105">
         <v>15.7</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" t="n">
-        <v>94.09999999999999</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>94.1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
         <v>150.4</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="n">
+    <row r="108" spans="1:1">
+      <c r="A108">
         <v>124.6</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" t="n">
+    <row r="109" spans="1:1">
+      <c r="A109">
         <v>118.2</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="n">
+    <row r="110" spans="1:1">
+      <c r="A110">
         <v>72.2</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="n">
+    <row r="111" spans="1:1">
+      <c r="A111">
         <v>100</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
+    <row r="112" spans="1:1">
+      <c r="A112">
         <v>118.1</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="n">
+    <row r="113" spans="1:1">
+      <c r="A113">
         <v>106.8</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="n">
+    <row r="114" spans="1:1">
+      <c r="A114">
         <v>55.4</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="n">
+    <row r="115" spans="1:1">
+      <c r="A115">
         <v>41.6</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>37.8</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
         <v>50.6</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="n">
+    <row r="119" spans="1:1">
+      <c r="A119">
         <v>14.9</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>39.3</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
         <v>120.9</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="n">
+    <row r="122" spans="1:1">
+      <c r="A122">
         <v>114</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="n">
+    <row r="123" spans="1:1">
+      <c r="A123">
         <v>111.2</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" t="n">
+    <row r="124" spans="1:1">
+      <c r="A124">
         <v>105.4</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" t="n">
+    <row r="125" spans="1:1">
+      <c r="A125">
         <v>126.3</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="n">
+    <row r="126" spans="1:1">
+      <c r="A126">
         <v>93.8</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="n">
+    <row r="127" spans="1:1">
+      <c r="A127">
         <v>123.8</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="n">
+    <row r="128" spans="1:1">
+      <c r="A128">
         <v>59.8</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="n">
+    <row r="129" spans="1:1">
+      <c r="A129">
         <v>44.3</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" t="n">
+    <row r="130" spans="1:1">
+      <c r="A130">
         <v>46</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="n">
+    <row r="131" spans="1:1">
+      <c r="A131">
         <v>36.1</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" t="n">
+    <row r="132" spans="1:1">
+      <c r="A132">
         <v>39.4</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="n">
+    <row r="133" spans="1:1">
+      <c r="A133">
         <v>73.7</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="n">
+    <row r="134" spans="1:1">
+      <c r="A134">
         <v>47.3</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
+    <row r="135" spans="1:1">
+      <c r="A135">
         <v>103.4</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>131.2</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>132.8</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>131.19999999999999</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>132.80000000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
         <v>129.6</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="n">
+    <row r="139" spans="1:1">
+      <c r="A139">
         <v>113.2</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>80.09999999999999</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>83.40000000000001</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>9.300000000000001</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>80.099999999999994</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>83.4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
         <v>62</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" t="n">
+    <row r="144" spans="1:1">
+      <c r="A144">
         <v>51.1</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="n">
+    <row r="145" spans="1:1">
+      <c r="A145">
         <v>103.7</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="n">
+    <row r="146" spans="1:1">
+      <c r="A146">
         <v>113.9</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>96.09999999999999</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>96.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
         <v>116.9</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="n">
+    <row r="149" spans="1:1">
+      <c r="A149">
         <v>102.6</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" t="n">
+    <row r="150" spans="1:1">
+      <c r="A150">
         <v>97.8</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" t="n">
+    <row r="151" spans="1:1">
+      <c r="A151">
         <v>66.2</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" t="n">
+    <row r="152" spans="1:1">
+      <c r="A152">
         <v>82.8</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="n">
+    <row r="153" spans="1:1">
+      <c r="A153">
         <v>41</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" t="n">
+    <row r="154" spans="1:1">
+      <c r="A154">
         <v>54.1</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" t="n">
+    <row r="155" spans="1:1">
+      <c r="A155">
         <v>84.7</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>67.40000000000001</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
         <v>39</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="n">
+    <row r="158" spans="1:1">
+      <c r="A158">
         <v>97.7</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" t="n">
+    <row r="159" spans="1:1">
+      <c r="A159">
         <v>88.8</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="n">
+    <row r="160" spans="1:1">
+      <c r="A160">
         <v>99</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>88.09999999999999</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>98.90000000000001</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>72.09999999999999</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>85.59999999999999</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>81.90000000000001</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>88.1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>98.9</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>85.6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>81.900000000000006</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
         <v>53.9</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" t="n">
+    <row r="167" spans="1:1">
+      <c r="A167">
         <v>80</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" t="n">
+    <row r="168" spans="1:1">
+      <c r="A168">
         <v>75.5</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="n">
+    <row r="169" spans="1:1">
+      <c r="A169">
         <v>49</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" t="n">
+    <row r="170" spans="1:1">
+      <c r="A170">
         <v>79.8</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>84.90000000000001</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>84.9</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
         <v>89.5</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>93.59999999999999</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>93.6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
         <v>85</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" t="n">
+    <row r="175" spans="1:1">
+      <c r="A175">
         <v>89.3</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" t="n">
+    <row r="176" spans="1:1">
+      <c r="A176">
         <v>92.8</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" t="n">
+    <row r="177" spans="1:1">
+      <c r="A177">
         <v>76.3</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" t="n">
+    <row r="178" spans="1:1">
+      <c r="A178">
         <v>116.3</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" t="n">
+    <row r="179" spans="1:1">
+      <c r="A179">
         <v>69.8</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" t="n">
+    <row r="180" spans="1:1">
+      <c r="A180">
         <v>80</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" t="n">
+    <row r="181" spans="1:1">
+      <c r="A181">
         <v>112.8</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" t="n">
+    <row r="182" spans="1:1">
+      <c r="A182">
         <v>90.2</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" t="n">
+    <row r="183" spans="1:1">
+      <c r="A183">
         <v>110.7</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" t="n">
+    <row r="184" spans="1:1">
+      <c r="A184">
         <v>106.4</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" t="n">
+    <row r="185" spans="1:1">
+      <c r="A185">
         <v>110.1</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="n">
+    <row r="186" spans="1:1">
+      <c r="A186">
         <v>104</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" t="n">
+    <row r="187" spans="1:1">
+      <c r="A187">
         <v>124.6</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>93.40000000000001</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>93.4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
         <v>139.6</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" t="n">
+    <row r="190" spans="1:1">
+      <c r="A190">
         <v>125</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" t="n">
+    <row r="191" spans="1:1">
+      <c r="A191">
         <v>153.4</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>142.3</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>142.30000000000001</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
         <v>115.1</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" t="n">
+    <row r="194" spans="1:1">
+      <c r="A194">
         <v>103.2</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" t="n">
+    <row r="195" spans="1:1">
+      <c r="A195">
         <v>81.5</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" t="n">
+    <row r="196" spans="1:1">
+      <c r="A196">
         <v>108.6</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>133.7</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>133.69999999999999</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
         <v>98.2</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" t="n">
+    <row r="199" spans="1:1">
+      <c r="A199">
         <v>113.7</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" t="n">
+    <row r="200" spans="1:1">
+      <c r="A200">
         <v>117.1</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" t="n">
+    <row r="201" spans="1:1">
+      <c r="A201">
         <v>121.3</v>
       </c>
     </row>
@@ -1469,133 +1469,109 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mean (a)</t>
-        </is>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="B1" s="2">
         <f>AVERAGE(Data!$A$2:$A$201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Median (a)</t>
-        </is>
+        <v>71.13600000000001</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <f>MEDIAN(Data!$A$2:$A$201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>90th percentile (a)</t>
-        </is>
+        <v>75.900000000000006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <f>_xlfn.PERCENTILE.INC(Data!$A$2:$A$201,0.9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Q1 (c)</t>
-        </is>
+        <v>116.72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="3">
         <f>_xlfn.QUARTILE.INC(Data!$A$2:$A$201,1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Q3 (c)</t>
-        </is>
+        <v>44.975000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B5" s="3">
         <f>_xlfn.QUARTILE.INC(Data!$A$2:$A$201,3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>IQR (c)</t>
-        </is>
+        <v>96.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="3">
         <f>B5-B4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>(b) Ninety percent of RMs had 2023 oat yields at or below about 117 bu/ac -- only the top tenth of RMs did better than that.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>(d) The mean (71.1) sits below the median (75.9), so the distribution is left-skewed: a tail of low-yield RMs pulls the mean down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Legend: colours mark question parts</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Part (a)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Part (b)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Part (c)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Part (d)</t>
-        </is>
+        <v>51.524999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="63.95" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" ht="63.95" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
